--- a/output/结果.xlsx
+++ b/output/结果.xlsx
@@ -330,6 +330,18 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -344,18 +356,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -372,21 +372,7 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -587,25 +573,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="19"/>
-      <tableStyleElement type="headerRow" dxfId="18"/>
-      <tableStyleElement type="totalRow" dxfId="17"/>
-      <tableStyleElement type="firstColumn" dxfId="16"/>
-      <tableStyleElement type="lastColumn" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstColumn" dxfId="14"/>
+      <tableStyleElement type="lastColumn" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="11"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="12"/>
-      <tableStyleElement type="totalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="9"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="8"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="7"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="6"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="5"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="4"/>
-      <tableStyleElement type="pageFieldValues" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="totalRow" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="6"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="4"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="3"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="2"/>
+      <tableStyleElement type="pageFieldValues" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -933,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ33"/>
+  <dimension ref="A1:AJ34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col width="37.6640625" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
@@ -1160,7 +1146,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="1" t="n"/>
-      <c r="G2" s="23">
+      <c r="G2" s="18">
         <f>F2/E2</f>
         <v/>
       </c>
@@ -1168,9 +1154,9 @@
         <v>14</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="23">
+        <v>2</v>
+      </c>
+      <c r="J2" s="18">
         <f>I2/H2</f>
         <v/>
       </c>
@@ -1178,9 +1164,9 @@
         <v>32</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="23">
+        <v>2</v>
+      </c>
+      <c r="M2" s="18">
         <f>L2/K2</f>
         <v/>
       </c>
@@ -1188,7 +1174,7 @@
         <v>14</v>
       </c>
       <c r="O2" s="1" t="n"/>
-      <c r="P2" s="23">
+      <c r="P2" s="18">
         <f>O2/N2</f>
         <v/>
       </c>
@@ -1196,9 +1182,9 @@
         <v>14</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" s="23">
+        <v>4</v>
+      </c>
+      <c r="S2" s="18">
         <f>R2/Q2</f>
         <v/>
       </c>
@@ -1206,9 +1192,9 @@
         <v>32</v>
       </c>
       <c r="U2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" s="23">
+        <v>4</v>
+      </c>
+      <c r="V2" s="18">
         <f>U2/T2</f>
         <v/>
       </c>
@@ -1274,7 +1260,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="n"/>
-      <c r="G3" s="23">
+      <c r="G3" s="18">
         <f>F3/E3</f>
         <v/>
       </c>
@@ -1282,9 +1268,9 @@
         <v>8</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="23">
+        <v>1</v>
+      </c>
+      <c r="J3" s="18">
         <f>I3/H3</f>
         <v/>
       </c>
@@ -1292,9 +1278,9 @@
         <v>18</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="23">
+        <v>1</v>
+      </c>
+      <c r="M3" s="18">
         <f>L3/K3</f>
         <v/>
       </c>
@@ -1302,7 +1288,7 @@
         <v>9</v>
       </c>
       <c r="O3" s="1" t="n"/>
-      <c r="P3" s="23">
+      <c r="P3" s="18">
         <f>O3/N3</f>
         <v/>
       </c>
@@ -1310,9 +1296,9 @@
         <v>8</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="23">
+        <v>2</v>
+      </c>
+      <c r="S3" s="18">
         <f>R3/Q3</f>
         <v/>
       </c>
@@ -1320,9 +1306,9 @@
         <v>18</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="23">
+        <v>2</v>
+      </c>
+      <c r="V3" s="18">
         <f>U3/T3</f>
         <v/>
       </c>
@@ -1388,7 +1374,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="1" t="n"/>
-      <c r="G4" s="23">
+      <c r="G4" s="18">
         <f>F4/E4</f>
         <v/>
       </c>
@@ -1396,9 +1382,9 @@
         <v>2</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="23">
+        <v>1</v>
+      </c>
+      <c r="J4" s="18">
         <f>I4/H4</f>
         <v/>
       </c>
@@ -1406,9 +1392,9 @@
         <v>5</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="23">
+        <v>1</v>
+      </c>
+      <c r="M4" s="18">
         <f>L4/K4</f>
         <v/>
       </c>
@@ -1416,7 +1402,7 @@
         <v>2</v>
       </c>
       <c r="O4" s="1" t="n"/>
-      <c r="P4" s="23">
+      <c r="P4" s="18">
         <f>O4/N4</f>
         <v/>
       </c>
@@ -1424,9 +1410,9 @@
         <v>2</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="23">
+        <v>2</v>
+      </c>
+      <c r="S4" s="18">
         <f>R4/Q4</f>
         <v/>
       </c>
@@ -1434,9 +1420,9 @@
         <v>5</v>
       </c>
       <c r="U4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="23">
+        <v>2</v>
+      </c>
+      <c r="V4" s="18">
         <f>U4/T4</f>
         <v/>
       </c>
@@ -1502,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="n"/>
-      <c r="G5" s="23">
+      <c r="G5" s="18">
         <f>F5/E5</f>
         <v/>
       </c>
@@ -1512,7 +1498,7 @@
       <c r="I5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="18">
         <f>I5/H5</f>
         <v/>
       </c>
@@ -1522,7 +1508,7 @@
       <c r="L5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="18">
         <f>L5/K5</f>
         <v/>
       </c>
@@ -1530,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="1" t="n"/>
-      <c r="P5" s="23">
+      <c r="P5" s="18">
         <f>O5/N5</f>
         <v/>
       </c>
@@ -1540,7 +1526,7 @@
       <c r="R5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="23">
+      <c r="S5" s="18">
         <f>R5/Q5</f>
         <v/>
       </c>
@@ -1550,7 +1536,7 @@
       <c r="U5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="23">
+      <c r="V5" s="18">
         <f>U5/T5</f>
         <v/>
       </c>
@@ -1594,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="n"/>
-      <c r="G6" s="23">
+      <c r="G6" s="18">
         <f>F6/E6</f>
         <v/>
       </c>
@@ -1604,7 +1590,7 @@
       <c r="I6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="23">
+      <c r="J6" s="18">
         <f>I6/H6</f>
         <v/>
       </c>
@@ -1614,7 +1600,7 @@
       <c r="L6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="18">
         <f>L6/K6</f>
         <v/>
       </c>
@@ -1622,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="n"/>
-      <c r="P6" s="23">
+      <c r="P6" s="18">
         <f>O6/N6</f>
         <v/>
       </c>
@@ -1632,7 +1618,7 @@
       <c r="R6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="23">
+      <c r="S6" s="18">
         <f>R6/Q6</f>
         <v/>
       </c>
@@ -1642,7 +1628,7 @@
       <c r="U6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="23">
+      <c r="V6" s="18">
         <f>U6/T6</f>
         <v/>
       </c>
@@ -1692,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="n"/>
-      <c r="G7" s="23">
+      <c r="G7" s="18">
         <f>F7/E7</f>
         <v/>
       </c>
@@ -1702,7 +1688,7 @@
       <c r="I7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="18">
         <f>I7/H7</f>
         <v/>
       </c>
@@ -1712,7 +1698,7 @@
       <c r="L7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="18">
         <f>L7/K7</f>
         <v/>
       </c>
@@ -1720,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="1" t="n"/>
-      <c r="P7" s="23">
+      <c r="P7" s="18">
         <f>O7/N7</f>
         <v/>
       </c>
@@ -1730,7 +1716,7 @@
       <c r="R7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="23">
+      <c r="S7" s="18">
         <f>R7/Q7</f>
         <v/>
       </c>
@@ -1740,7 +1726,7 @@
       <c r="U7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="23">
+      <c r="V7" s="18">
         <f>U7/T7</f>
         <v/>
       </c>
@@ -1794,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="n"/>
-      <c r="G8" s="23">
+      <c r="G8" s="18">
         <f>F8/E8</f>
         <v/>
       </c>
@@ -1804,7 +1790,7 @@
       <c r="I8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="18">
         <f>I8/H8</f>
         <v/>
       </c>
@@ -1814,7 +1800,7 @@
       <c r="L8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="18">
         <f>L8/K8</f>
         <v/>
       </c>
@@ -1822,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="n"/>
-      <c r="P8" s="23">
+      <c r="P8" s="18">
         <f>O8/N8</f>
         <v/>
       </c>
@@ -1832,7 +1818,7 @@
       <c r="R8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="23">
+      <c r="S8" s="18">
         <f>R8/Q8</f>
         <v/>
       </c>
@@ -1842,7 +1828,7 @@
       <c r="U8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="23">
+      <c r="V8" s="18">
         <f>U8/T8</f>
         <v/>
       </c>
@@ -1892,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="n"/>
-      <c r="G9" s="23">
+      <c r="G9" s="18">
         <f>F9/E9</f>
         <v/>
       </c>
@@ -1902,7 +1888,7 @@
       <c r="I9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="18">
         <f>I9/H9</f>
         <v/>
       </c>
@@ -1912,7 +1898,7 @@
       <c r="L9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="23">
+      <c r="M9" s="18">
         <f>L9/K9</f>
         <v/>
       </c>
@@ -1920,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="n"/>
-      <c r="P9" s="23">
+      <c r="P9" s="18">
         <f>O9/N9</f>
         <v/>
       </c>
@@ -1930,7 +1916,7 @@
       <c r="R9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="23">
+      <c r="S9" s="18">
         <f>R9/Q9</f>
         <v/>
       </c>
@@ -1940,7 +1926,7 @@
       <c r="U9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="23">
+      <c r="V9" s="18">
         <f>U9/T9</f>
         <v/>
       </c>
@@ -1986,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="n"/>
-      <c r="G10" s="23">
+      <c r="G10" s="18">
         <f>F10/E10</f>
         <v/>
       </c>
@@ -1996,7 +1982,7 @@
       <c r="I10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="18">
         <f>I10/H10</f>
         <v/>
       </c>
@@ -2006,7 +1992,7 @@
       <c r="L10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="23">
+      <c r="M10" s="18">
         <f>L10/K10</f>
         <v/>
       </c>
@@ -2014,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="1" t="n"/>
-      <c r="P10" s="23">
+      <c r="P10" s="18">
         <f>O10/N10</f>
         <v/>
       </c>
@@ -2024,7 +2010,7 @@
       <c r="R10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S10" s="23">
+      <c r="S10" s="18">
         <f>R10/Q10</f>
         <v/>
       </c>
@@ -2034,7 +2020,7 @@
       <c r="U10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="23">
+      <c r="V10" s="18">
         <f>U10/T10</f>
         <v/>
       </c>
@@ -2084,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="n"/>
-      <c r="G11" s="23">
+      <c r="G11" s="18">
         <f>F11/E11</f>
         <v/>
       </c>
@@ -2094,7 +2080,7 @@
       <c r="I11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="18">
         <f>I11/H11</f>
         <v/>
       </c>
@@ -2104,7 +2090,7 @@
       <c r="L11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="23">
+      <c r="M11" s="18">
         <f>L11/K11</f>
         <v/>
       </c>
@@ -2112,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="1" t="n"/>
-      <c r="P11" s="23">
+      <c r="P11" s="18">
         <f>O11/N11</f>
         <v/>
       </c>
@@ -2122,7 +2108,7 @@
       <c r="R11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="23">
+      <c r="S11" s="18">
         <f>R11/Q11</f>
         <v/>
       </c>
@@ -2132,7 +2118,7 @@
       <c r="U11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="23">
+      <c r="V11" s="18">
         <f>U11/T11</f>
         <v/>
       </c>
@@ -2180,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="n"/>
-      <c r="G12" s="23">
+      <c r="G12" s="18">
         <f>F12/E12</f>
         <v/>
       </c>
@@ -2190,7 +2176,7 @@
       <c r="I12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="18">
         <f>I12/H12</f>
         <v/>
       </c>
@@ -2200,7 +2186,7 @@
       <c r="L12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="23">
+      <c r="M12" s="18">
         <f>L12/K12</f>
         <v/>
       </c>
@@ -2208,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="1" t="n"/>
-      <c r="P12" s="23">
+      <c r="P12" s="18">
         <f>O12/N12</f>
         <v/>
       </c>
@@ -2218,7 +2204,7 @@
       <c r="R12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="23">
+      <c r="S12" s="18">
         <f>R12/Q12</f>
         <v/>
       </c>
@@ -2228,7 +2214,7 @@
       <c r="U12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="23">
+      <c r="V12" s="18">
         <f>U12/T12</f>
         <v/>
       </c>
@@ -2274,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="1" t="n"/>
-      <c r="G13" s="23">
+      <c r="G13" s="18">
         <f>F13/E13</f>
         <v/>
       </c>
@@ -2284,7 +2270,7 @@
       <c r="I13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="18">
         <f>I13/H13</f>
         <v/>
       </c>
@@ -2294,7 +2280,7 @@
       <c r="L13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="23">
+      <c r="M13" s="18">
         <f>L13/K13</f>
         <v/>
       </c>
@@ -2302,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="1" t="n"/>
-      <c r="P13" s="23">
+      <c r="P13" s="18">
         <f>O13/N13</f>
         <v/>
       </c>
@@ -2312,7 +2298,7 @@
       <c r="R13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="23">
+      <c r="S13" s="18">
         <f>R13/Q13</f>
         <v/>
       </c>
@@ -2322,7 +2308,7 @@
       <c r="U13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="23">
+      <c r="V13" s="18">
         <f>U13/T13</f>
         <v/>
       </c>
@@ -2368,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="1" t="n"/>
-      <c r="G14" s="23">
+      <c r="G14" s="18">
         <f>F14/E14</f>
         <v/>
       </c>
@@ -2378,7 +2364,7 @@
       <c r="I14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="18">
         <f>I14/H14</f>
         <v/>
       </c>
@@ -2388,7 +2374,7 @@
       <c r="L14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="23">
+      <c r="M14" s="18">
         <f>L14/K14</f>
         <v/>
       </c>
@@ -2396,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="1" t="n"/>
-      <c r="P14" s="23">
+      <c r="P14" s="18">
         <f>O14/N14</f>
         <v/>
       </c>
@@ -2406,7 +2392,7 @@
       <c r="R14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="23">
+      <c r="S14" s="18">
         <f>R14/Q14</f>
         <v/>
       </c>
@@ -2416,7 +2402,7 @@
       <c r="U14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="23">
+      <c r="V14" s="18">
         <f>U14/T14</f>
         <v/>
       </c>
@@ -2464,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="1" t="n"/>
-      <c r="G15" s="23">
+      <c r="G15" s="18">
         <f>F15/E15</f>
         <v/>
       </c>
@@ -2474,7 +2460,7 @@
       <c r="I15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="23">
+      <c r="J15" s="18">
         <f>I15/H15</f>
         <v/>
       </c>
@@ -2484,7 +2470,7 @@
       <c r="L15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="23">
+      <c r="M15" s="18">
         <f>L15/K15</f>
         <v/>
       </c>
@@ -2492,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="1" t="n"/>
-      <c r="P15" s="23">
+      <c r="P15" s="18">
         <f>O15/N15</f>
         <v/>
       </c>
@@ -2502,7 +2488,7 @@
       <c r="R15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="23">
+      <c r="S15" s="18">
         <f>R15/Q15</f>
         <v/>
       </c>
@@ -2512,7 +2498,7 @@
       <c r="U15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="23">
+      <c r="V15" s="18">
         <f>U15/T15</f>
         <v/>
       </c>
@@ -2558,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="1" t="n"/>
-      <c r="G16" s="23">
+      <c r="G16" s="18">
         <f>F16/E16</f>
         <v/>
       </c>
@@ -2568,7 +2554,7 @@
       <c r="I16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="23">
+      <c r="J16" s="18">
         <f>I16/H16</f>
         <v/>
       </c>
@@ -2578,7 +2564,7 @@
       <c r="L16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="23">
+      <c r="M16" s="18">
         <f>L16/K16</f>
         <v/>
       </c>
@@ -2586,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="1" t="n"/>
-      <c r="P16" s="23">
+      <c r="P16" s="18">
         <f>O16/N16</f>
         <v/>
       </c>
@@ -2596,7 +2582,7 @@
       <c r="R16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S16" s="23">
+      <c r="S16" s="18">
         <f>R16/Q16</f>
         <v/>
       </c>
@@ -2606,7 +2592,7 @@
       <c r="U16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="23">
+      <c r="V16" s="18">
         <f>U16/T16</f>
         <v/>
       </c>
@@ -2654,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="1" t="n"/>
-      <c r="G17" s="23">
+      <c r="G17" s="18">
         <f>F17/E17</f>
         <v/>
       </c>
@@ -2664,7 +2650,7 @@
       <c r="I17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="23">
+      <c r="J17" s="18">
         <f>I17/H17</f>
         <v/>
       </c>
@@ -2674,7 +2660,7 @@
       <c r="L17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="23">
+      <c r="M17" s="18">
         <f>L17/K17</f>
         <v/>
       </c>
@@ -2682,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="1" t="n"/>
-      <c r="P17" s="23">
+      <c r="P17" s="18">
         <f>O17/N17</f>
         <v/>
       </c>
@@ -2692,7 +2678,7 @@
       <c r="R17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S17" s="23">
+      <c r="S17" s="18">
         <f>R17/Q17</f>
         <v/>
       </c>
@@ -2702,7 +2688,7 @@
       <c r="U17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="23">
+      <c r="V17" s="18">
         <f>U17/T17</f>
         <v/>
       </c>
@@ -2746,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="1" t="n"/>
-      <c r="G18" s="23">
+      <c r="G18" s="18">
         <f>F18/E18</f>
         <v/>
       </c>
@@ -2756,7 +2742,7 @@
       <c r="I18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="23">
+      <c r="J18" s="18">
         <f>I18/H18</f>
         <v/>
       </c>
@@ -2766,7 +2752,7 @@
       <c r="L18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="23">
+      <c r="M18" s="18">
         <f>L18/K18</f>
         <v/>
       </c>
@@ -2774,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="1" t="n"/>
-      <c r="P18" s="23">
+      <c r="P18" s="18">
         <f>O18/N18</f>
         <v/>
       </c>
@@ -2784,7 +2770,7 @@
       <c r="R18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S18" s="23">
+      <c r="S18" s="18">
         <f>R18/Q18</f>
         <v/>
       </c>
@@ -2794,7 +2780,7 @@
       <c r="U18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="23">
+      <c r="V18" s="18">
         <f>U18/T18</f>
         <v/>
       </c>
@@ -2838,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="1" t="n"/>
-      <c r="G19" s="23">
+      <c r="G19" s="18">
         <f>F19/E19</f>
         <v/>
       </c>
@@ -2848,7 +2834,7 @@
       <c r="I19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="18">
         <f>I19/H19</f>
         <v/>
       </c>
@@ -2858,7 +2844,7 @@
       <c r="L19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="23">
+      <c r="M19" s="18">
         <f>L19/K19</f>
         <v/>
       </c>
@@ -2866,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="1" t="n"/>
-      <c r="P19" s="23">
+      <c r="P19" s="18">
         <f>O19/N19</f>
         <v/>
       </c>
@@ -2876,7 +2862,7 @@
       <c r="R19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="23">
+      <c r="S19" s="18">
         <f>R19/Q19</f>
         <v/>
       </c>
@@ -2886,7 +2872,7 @@
       <c r="U19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="23">
+      <c r="V19" s="18">
         <f>U19/T19</f>
         <v/>
       </c>
@@ -2932,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="1" t="n"/>
-      <c r="G20" s="23">
+      <c r="G20" s="18">
         <f>F20/E20</f>
         <v/>
       </c>
@@ -2942,7 +2928,7 @@
       <c r="I20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="23">
+      <c r="J20" s="18">
         <f>I20/H20</f>
         <v/>
       </c>
@@ -2952,7 +2938,7 @@
       <c r="L20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="23">
+      <c r="M20" s="18">
         <f>L20/K20</f>
         <v/>
       </c>
@@ -2960,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="1" t="n"/>
-      <c r="P20" s="23">
+      <c r="P20" s="18">
         <f>O20/N20</f>
         <v/>
       </c>
@@ -2970,7 +2956,7 @@
       <c r="R20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S20" s="23">
+      <c r="S20" s="18">
         <f>R20/Q20</f>
         <v/>
       </c>
@@ -2980,7 +2966,7 @@
       <c r="U20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="23">
+      <c r="V20" s="18">
         <f>U20/T20</f>
         <v/>
       </c>
@@ -3020,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="1" t="n"/>
-      <c r="G21" s="23">
+      <c r="G21" s="18">
         <f>F21/E21</f>
         <v/>
       </c>
@@ -3030,7 +3016,7 @@
       <c r="I21" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="23">
+      <c r="J21" s="18">
         <f>I21/H21</f>
         <v/>
       </c>
@@ -3040,7 +3026,7 @@
       <c r="L21" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="23">
+      <c r="M21" s="18">
         <f>L21/K21</f>
         <v/>
       </c>
@@ -3048,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="1" t="n"/>
-      <c r="P21" s="23">
+      <c r="P21" s="18">
         <f>O21/N21</f>
         <v/>
       </c>
@@ -3058,7 +3044,7 @@
       <c r="R21" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S21" s="23">
+      <c r="S21" s="18">
         <f>R21/Q21</f>
         <v/>
       </c>
@@ -3068,7 +3054,7 @@
       <c r="U21" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="23">
+      <c r="V21" s="18">
         <f>U21/T21</f>
         <v/>
       </c>
@@ -3112,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="1" t="n"/>
-      <c r="G22" s="23">
+      <c r="G22" s="18">
         <f>F22/E22</f>
         <v/>
       </c>
@@ -3122,7 +3108,7 @@
       <c r="I22" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="23">
+      <c r="J22" s="18">
         <f>I22/H22</f>
         <v/>
       </c>
@@ -3132,7 +3118,7 @@
       <c r="L22" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="23">
+      <c r="M22" s="18">
         <f>L22/K22</f>
         <v/>
       </c>
@@ -3140,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="1" t="n"/>
-      <c r="P22" s="23">
+      <c r="P22" s="18">
         <f>O22/N22</f>
         <v/>
       </c>
@@ -3150,7 +3136,7 @@
       <c r="R22" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S22" s="23">
+      <c r="S22" s="18">
         <f>R22/Q22</f>
         <v/>
       </c>
@@ -3160,7 +3146,7 @@
       <c r="U22" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="23">
+      <c r="V22" s="18">
         <f>U22/T22</f>
         <v/>
       </c>
@@ -3204,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="1" t="n"/>
-      <c r="G23" s="23">
+      <c r="G23" s="18">
         <f>F23/E23</f>
         <v/>
       </c>
@@ -3214,7 +3200,7 @@
       <c r="I23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="23">
+      <c r="J23" s="18">
         <f>I23/H23</f>
         <v/>
       </c>
@@ -3224,7 +3210,7 @@
       <c r="L23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="23">
+      <c r="M23" s="18">
         <f>L23/K23</f>
         <v/>
       </c>
@@ -3232,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="1" t="n"/>
-      <c r="P23" s="23">
+      <c r="P23" s="18">
         <f>O23/N23</f>
         <v/>
       </c>
@@ -3242,7 +3228,7 @@
       <c r="R23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="23">
+      <c r="S23" s="18">
         <f>R23/Q23</f>
         <v/>
       </c>
@@ -3252,7 +3238,7 @@
       <c r="U23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="23">
+      <c r="V23" s="18">
         <f>U23/T23</f>
         <v/>
       </c>
@@ -3294,7 +3280,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="1" t="n"/>
-      <c r="G24" s="23">
+      <c r="G24" s="18">
         <f>F24/E24</f>
         <v/>
       </c>
@@ -3304,7 +3290,7 @@
       <c r="I24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="23">
+      <c r="J24" s="18">
         <f>I24/H24</f>
         <v/>
       </c>
@@ -3314,7 +3300,7 @@
       <c r="L24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="23">
+      <c r="M24" s="18">
         <f>L24/K24</f>
         <v/>
       </c>
@@ -3322,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="1" t="n"/>
-      <c r="P24" s="23">
+      <c r="P24" s="18">
         <f>O24/N24</f>
         <v/>
       </c>
@@ -3332,7 +3318,7 @@
       <c r="R24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="23">
+      <c r="S24" s="18">
         <f>R24/Q24</f>
         <v/>
       </c>
@@ -3342,7 +3328,7 @@
       <c r="U24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="23">
+      <c r="V24" s="18">
         <f>U24/T24</f>
         <v/>
       </c>
@@ -3382,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="1" t="n"/>
-      <c r="G25" s="23">
+      <c r="G25" s="18">
         <f>F25/E25</f>
         <v/>
       </c>
@@ -3392,7 +3378,7 @@
       <c r="I25" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="23">
+      <c r="J25" s="18">
         <f>I25/H25</f>
         <v/>
       </c>
@@ -3402,7 +3388,7 @@
       <c r="L25" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="23">
+      <c r="M25" s="18">
         <f>L25/K25</f>
         <v/>
       </c>
@@ -3410,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="1" t="n"/>
-      <c r="P25" s="23">
+      <c r="P25" s="18">
         <f>O25/N25</f>
         <v/>
       </c>
@@ -3420,7 +3406,7 @@
       <c r="R25" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="23">
+      <c r="S25" s="18">
         <f>R25/Q25</f>
         <v/>
       </c>
@@ -3430,7 +3416,7 @@
       <c r="U25" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="23">
+      <c r="V25" s="18">
         <f>U25/T25</f>
         <v/>
       </c>
@@ -3472,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="1" t="n"/>
-      <c r="G26" s="23">
+      <c r="G26" s="18">
         <f>F26/E26</f>
         <v/>
       </c>
@@ -3482,7 +3468,7 @@
       <c r="I26" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="23">
+      <c r="J26" s="18">
         <f>I26/H26</f>
         <v/>
       </c>
@@ -3492,7 +3478,7 @@
       <c r="L26" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="23">
+      <c r="M26" s="18">
         <f>L26/K26</f>
         <v/>
       </c>
@@ -3500,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="O26" s="1" t="n"/>
-      <c r="P26" s="23">
+      <c r="P26" s="18">
         <f>O26/N26</f>
         <v/>
       </c>
@@ -3510,7 +3496,7 @@
       <c r="R26" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S26" s="23">
+      <c r="S26" s="18">
         <f>R26/Q26</f>
         <v/>
       </c>
@@ -3520,7 +3506,7 @@
       <c r="U26" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="23">
+      <c r="V26" s="18">
         <f>U26/T26</f>
         <v/>
       </c>
@@ -3562,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="1" t="n"/>
-      <c r="G27" s="23">
+      <c r="G27" s="18">
         <f>F27/E27</f>
         <v/>
       </c>
@@ -3572,7 +3558,7 @@
       <c r="I27" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="23">
+      <c r="J27" s="18">
         <f>I27/H27</f>
         <v/>
       </c>
@@ -3582,7 +3568,7 @@
       <c r="L27" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="23">
+      <c r="M27" s="18">
         <f>L27/K27</f>
         <v/>
       </c>
@@ -3590,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="1" t="n"/>
-      <c r="P27" s="23">
+      <c r="P27" s="18">
         <f>O27/N27</f>
         <v/>
       </c>
@@ -3600,7 +3586,7 @@
       <c r="R27" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S27" s="23">
+      <c r="S27" s="18">
         <f>R27/Q27</f>
         <v/>
       </c>
@@ -3610,7 +3596,7 @@
       <c r="U27" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="23">
+      <c r="V27" s="18">
         <f>U27/T27</f>
         <v/>
       </c>
@@ -3652,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="1" t="n"/>
-      <c r="G28" s="23">
+      <c r="G28" s="18">
         <f>F28/E28</f>
         <v/>
       </c>
@@ -3662,7 +3648,7 @@
       <c r="I28" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="23">
+      <c r="J28" s="18">
         <f>I28/H28</f>
         <v/>
       </c>
@@ -3672,7 +3658,7 @@
       <c r="L28" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="23">
+      <c r="M28" s="18">
         <f>L28/K28</f>
         <v/>
       </c>
@@ -3680,7 +3666,7 @@
         <v>0</v>
       </c>
       <c r="O28" s="1" t="n"/>
-      <c r="P28" s="23">
+      <c r="P28" s="18">
         <f>O28/N28</f>
         <v/>
       </c>
@@ -3690,7 +3676,7 @@
       <c r="R28" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S28" s="23">
+      <c r="S28" s="18">
         <f>R28/Q28</f>
         <v/>
       </c>
@@ -3700,7 +3686,7 @@
       <c r="U28" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="23">
+      <c r="V28" s="18">
         <f>U28/T28</f>
         <v/>
       </c>
@@ -3742,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="1" t="n"/>
-      <c r="G29" s="23">
+      <c r="G29" s="18">
         <f>F29/E29</f>
         <v/>
       </c>
@@ -3752,7 +3738,7 @@
       <c r="I29" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="23">
+      <c r="J29" s="18">
         <f>I29/H29</f>
         <v/>
       </c>
@@ -3762,7 +3748,7 @@
       <c r="L29" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="23">
+      <c r="M29" s="18">
         <f>L29/K29</f>
         <v/>
       </c>
@@ -3770,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="1" t="n"/>
-      <c r="P29" s="23">
+      <c r="P29" s="18">
         <f>O29/N29</f>
         <v/>
       </c>
@@ -3780,7 +3766,7 @@
       <c r="R29" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="23">
+      <c r="S29" s="18">
         <f>R29/Q29</f>
         <v/>
       </c>
@@ -3790,7 +3776,7 @@
       <c r="U29" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="23">
+      <c r="V29" s="18">
         <f>U29/T29</f>
         <v/>
       </c>
@@ -3832,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="1" t="n"/>
-      <c r="G30" s="23">
+      <c r="G30" s="18">
         <f>F30/E30</f>
         <v/>
       </c>
@@ -3842,7 +3828,7 @@
       <c r="I30" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="23">
+      <c r="J30" s="18">
         <f>I30/H30</f>
         <v/>
       </c>
@@ -3852,7 +3838,7 @@
       <c r="L30" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="23">
+      <c r="M30" s="18">
         <f>L30/K30</f>
         <v/>
       </c>
@@ -3860,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="1" t="n"/>
-      <c r="P30" s="23">
+      <c r="P30" s="18">
         <f>O30/N30</f>
         <v/>
       </c>
@@ -3870,7 +3856,7 @@
       <c r="R30" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="23">
+      <c r="S30" s="18">
         <f>R30/Q30</f>
         <v/>
       </c>
@@ -3880,7 +3866,7 @@
       <c r="U30" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="23">
+      <c r="V30" s="18">
         <f>U30/T30</f>
         <v/>
       </c>
@@ -3922,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="1" t="n"/>
-      <c r="G31" s="23">
+      <c r="G31" s="18">
         <f>F31/E31</f>
         <v/>
       </c>
@@ -3932,7 +3918,7 @@
       <c r="I31" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="23">
+      <c r="J31" s="18">
         <f>I31/H31</f>
         <v/>
       </c>
@@ -3942,7 +3928,7 @@
       <c r="L31" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="23">
+      <c r="M31" s="18">
         <f>L31/K31</f>
         <v/>
       </c>
@@ -3950,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="O31" s="1" t="n"/>
-      <c r="P31" s="23">
+      <c r="P31" s="18">
         <f>O31/N31</f>
         <v/>
       </c>
@@ -3960,7 +3946,7 @@
       <c r="R31" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S31" s="23">
+      <c r="S31" s="18">
         <f>R31/Q31</f>
         <v/>
       </c>
@@ -3970,7 +3956,7 @@
       <c r="U31" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="23">
+      <c r="V31" s="18">
         <f>U31/T31</f>
         <v/>
       </c>
@@ -4012,7 +3998,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="1" t="n"/>
-      <c r="G32" s="23">
+      <c r="G32" s="18">
         <f>F32/E32</f>
         <v/>
       </c>
@@ -4022,7 +4008,7 @@
       <c r="I32" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="23">
+      <c r="J32" s="18">
         <f>I32/H32</f>
         <v/>
       </c>
@@ -4032,7 +4018,7 @@
       <c r="L32" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="23">
+      <c r="M32" s="18">
         <f>L32/K32</f>
         <v/>
       </c>
@@ -4040,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="1" t="n"/>
-      <c r="P32" s="23">
+      <c r="P32" s="18">
         <f>O32/N32</f>
         <v/>
       </c>
@@ -4050,7 +4036,7 @@
       <c r="R32" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S32" s="23">
+      <c r="S32" s="18">
         <f>R32/Q32</f>
         <v/>
       </c>
@@ -4060,7 +4046,7 @@
       <c r="U32" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="23">
+      <c r="V32" s="18">
         <f>U32/T32</f>
         <v/>
       </c>
@@ -4084,154 +4070,256 @@
       <c r="AJ32" s="1" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="25">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>云南九机电子产品有限公司</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1" t="n"/>
+      <c r="G33" s="18">
+        <f>F33/E33</f>
+        <v/>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="18">
+        <f>I33/H33</f>
+        <v/>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="18">
+        <f>L33/K33</f>
+        <v/>
+      </c>
+      <c r="N33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1" t="n"/>
+      <c r="P33" s="18">
+        <f>O33/N33</f>
+        <v/>
+      </c>
+      <c r="Q33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="S33" s="18">
+        <f>R33/Q33</f>
+        <v/>
+      </c>
+      <c r="T33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V33" s="18">
+        <f>U33/T33</f>
+        <v/>
+      </c>
+      <c r="W33" s="1" t="n"/>
+      <c r="X33" s="1" t="n"/>
+      <c r="Y33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="1" t="n"/>
+      <c r="AA33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="1" t="n"/>
+      <c r="AC33" s="1" t="n"/>
+      <c r="AD33" s="1" t="n"/>
+      <c r="AE33" s="1" t="n"/>
+      <c r="AF33" s="1" t="n"/>
+      <c r="AG33" s="1" t="n"/>
+      <c r="AH33" s="1" t="n"/>
+      <c r="AI33" s="1" t="n"/>
+      <c r="AJ33" s="1" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="25">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>总计</t>
         </is>
       </c>
-      <c r="B33" s="2">
+      <c r="B34" s="2">
         <f>SUM(B2:B32)</f>
         <v/>
       </c>
-      <c r="C33" s="2">
+      <c r="C34" s="2">
         <f>SUM(C2:C32)</f>
         <v/>
       </c>
-      <c r="D33" s="2">
+      <c r="D34" s="2">
         <f>SUM(D2:D32)</f>
         <v/>
       </c>
-      <c r="E33" s="2">
+      <c r="E34" s="2">
         <f>SUM(E2:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="2">
+      <c r="F34" s="2">
         <f>SUM(F2:F32)</f>
         <v/>
       </c>
-      <c r="G33" s="24">
-        <f>F33/E33</f>
-        <v/>
-      </c>
-      <c r="H33" s="2">
+      <c r="G34" s="19">
+        <f>F34/E34</f>
+        <v/>
+      </c>
+      <c r="H34" s="2">
         <f>SUM(H2:H32)</f>
         <v/>
       </c>
-      <c r="I33" s="2">
+      <c r="I34" s="2">
         <f>SUM(I2:I32)</f>
         <v/>
       </c>
-      <c r="J33" s="24">
-        <f>I33/H33</f>
-        <v/>
-      </c>
-      <c r="K33" s="2">
+      <c r="J34" s="19">
+        <f>I34/H34</f>
+        <v/>
+      </c>
+      <c r="K34" s="2">
         <f>SUM(K2:K32)</f>
         <v/>
       </c>
-      <c r="L33" s="2">
+      <c r="L34" s="2">
         <f>SUM(L2:L32)</f>
         <v/>
       </c>
-      <c r="M33" s="24">
-        <f>L33/K33</f>
-        <v/>
-      </c>
-      <c r="N33" s="2">
+      <c r="M34" s="19">
+        <f>L34/K34</f>
+        <v/>
+      </c>
+      <c r="N34" s="2">
         <f>SUM(N2:N32)</f>
         <v/>
       </c>
-      <c r="O33" s="2">
+      <c r="O34" s="2">
         <f>SUM(O2:O32)</f>
         <v/>
       </c>
-      <c r="P33" s="24">
-        <f>O33/N33</f>
-        <v/>
-      </c>
-      <c r="Q33" s="2">
+      <c r="P34" s="19">
+        <f>O34/N34</f>
+        <v/>
+      </c>
+      <c r="Q34" s="2">
         <f>SUM(Q2:Q32)</f>
         <v/>
       </c>
-      <c r="R33" s="2">
+      <c r="R34" s="2">
         <f>SUM(R2:R32)</f>
         <v/>
       </c>
-      <c r="S33" s="24">
-        <f>R33/Q33</f>
-        <v/>
-      </c>
-      <c r="T33" s="2">
+      <c r="S34" s="19">
+        <f>R34/Q34</f>
+        <v/>
+      </c>
+      <c r="T34" s="2">
         <f>SUM(T2:T32)</f>
         <v/>
       </c>
-      <c r="U33" s="2">
+      <c r="U34" s="2">
         <f>SUM(U2:U32)</f>
         <v/>
       </c>
-      <c r="V33" s="24">
-        <f>U33/T33</f>
-        <v/>
-      </c>
-      <c r="W33" s="2">
+      <c r="V34" s="19">
+        <f>U34/T34</f>
+        <v/>
+      </c>
+      <c r="W34" s="2">
         <f>SUM(W2:W32)</f>
         <v/>
       </c>
-      <c r="X33" s="2">
+      <c r="X34" s="2">
         <f>SUM(X2:X32)</f>
         <v/>
       </c>
-      <c r="Y33" s="2">
+      <c r="Y34" s="2">
         <f>SUM(Y2:Y32)</f>
         <v/>
       </c>
-      <c r="Z33" s="2">
+      <c r="Z34" s="2">
         <f>SUM(Z2:Z32)</f>
         <v/>
       </c>
-      <c r="AA33" s="2">
+      <c r="AA34" s="2">
         <f>SUM(AA2:AA32)</f>
         <v/>
       </c>
-      <c r="AB33" s="2">
+      <c r="AB34" s="2">
         <f>SUM(AB2:AB32)</f>
         <v/>
       </c>
-      <c r="AC33" s="2">
+      <c r="AC34" s="2">
         <f>SUM(AC2:AC32)</f>
         <v/>
       </c>
-      <c r="AD33" s="2">
+      <c r="AD34" s="2">
         <f>SUM(AD2:AD32)</f>
         <v/>
       </c>
-      <c r="AE33" s="2">
+      <c r="AE34" s="2">
         <f>SUM(AE2:AE32)</f>
         <v/>
       </c>
-      <c r="AF33" s="2">
+      <c r="AF34" s="2">
         <f>SUM(AF2:AF32)</f>
         <v/>
       </c>
-      <c r="AG33" s="2">
+      <c r="AG34" s="2">
         <f>SUM(AG2:AG32)</f>
         <v/>
       </c>
-      <c r="AH33" s="2">
+      <c r="AH34" s="2">
         <f>SUM(AH2:AH32)</f>
         <v/>
       </c>
-      <c r="AI33" s="2">
+      <c r="AI34" s="2">
         <f>SUM(AI2:AI32)</f>
         <v/>
       </c>
-      <c r="AJ33" s="2">
+      <c r="AJ34" s="2">
         <f>SUM(AJ2:AJ32)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J32">
+  <conditionalFormatting sqref="G2:G33">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J33">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -4243,7 +4331,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M32">
+  <conditionalFormatting sqref="M2:M33">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -4255,7 +4343,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P32">
+  <conditionalFormatting sqref="P2:P33">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -4267,7 +4355,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S32">
+  <conditionalFormatting sqref="S2:S33">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -4279,20 +4367,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V32">
+  <conditionalFormatting sqref="V2:V33">
     <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G32">
-    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4321,7 +4397,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="25">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>门店名称</t>
         </is>
@@ -4336,7 +4412,7 @@
           <t>督导</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">畅享 90 Plus </t>
         </is>
@@ -4347,7 +4423,7 @@
       <c r="H1" s="27" t="n"/>
       <c r="I1" s="27" t="n"/>
       <c r="J1" s="28" t="n"/>
-      <c r="K1" s="17" t="inlineStr">
+      <c r="K1" s="21" t="inlineStr">
         <is>
           <t>畅享 90 Pro Max</t>
         </is>
@@ -4456,7 +4532,7 @@
       <c r="E3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="16">
         <f>E3/D3</f>
         <v/>
       </c>
@@ -4466,7 +4542,7 @@
       <c r="H3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="16">
         <f>H3/G3</f>
         <v/>
       </c>
@@ -4477,9 +4553,9 @@
         <v>2</v>
       </c>
       <c r="L3" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="21">
+        <v>0</v>
+      </c>
+      <c r="M3" s="16">
         <f>L3/K3</f>
         <v/>
       </c>
@@ -4487,9 +4563,9 @@
         <v>4</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="21">
+        <v>0</v>
+      </c>
+      <c r="P3" s="16">
         <f>O3/N3</f>
         <v/>
       </c>
@@ -4519,7 +4595,7 @@
       <c r="E4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="16">
         <f>E4/D4</f>
         <v/>
       </c>
@@ -4529,7 +4605,7 @@
       <c r="H4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="16">
         <f>H4/G4</f>
         <v/>
       </c>
@@ -4540,9 +4616,9 @@
         <v>3</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="21">
+        <v>2</v>
+      </c>
+      <c r="M4" s="16">
         <f>L4/K4</f>
         <v/>
       </c>
@@ -4550,9 +4626,9 @@
         <v>7</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="21">
+        <v>2</v>
+      </c>
+      <c r="P4" s="16">
         <f>O4/N4</f>
         <v/>
       </c>
@@ -4582,7 +4658,7 @@
       <c r="E5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="16">
         <f>E5/D5</f>
         <v/>
       </c>
@@ -4592,7 +4668,7 @@
       <c r="H5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="16">
         <f>H5/G5</f>
         <v/>
       </c>
@@ -4603,9 +4679,9 @@
         <v>1</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="21">
+        <v>1</v>
+      </c>
+      <c r="M5" s="16">
         <f>L5/K5</f>
         <v/>
       </c>
@@ -4613,9 +4689,9 @@
         <v>3</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="21">
+        <v>1</v>
+      </c>
+      <c r="P5" s="16">
         <f>O5/N5</f>
         <v/>
       </c>
@@ -4645,7 +4721,7 @@
       <c r="E6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="16">
         <f>E6/D6</f>
         <v/>
       </c>
@@ -4655,7 +4731,7 @@
       <c r="H6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="16">
         <f>H6/G6</f>
         <v/>
       </c>
@@ -4668,7 +4744,7 @@
       <c r="L6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="21">
+      <c r="M6" s="16">
         <f>L6/K6</f>
         <v/>
       </c>
@@ -4678,7 +4754,7 @@
       <c r="O6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="21">
+      <c r="P6" s="16">
         <f>O6/N6</f>
         <v/>
       </c>
@@ -4704,7 +4780,7 @@
       <c r="E7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="16">
         <f>E7/D7</f>
         <v/>
       </c>
@@ -4714,7 +4790,7 @@
       <c r="H7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="16">
         <f>H7/G7</f>
         <v/>
       </c>
@@ -4727,7 +4803,7 @@
       <c r="L7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="21">
+      <c r="M7" s="16">
         <f>L7/K7</f>
         <v/>
       </c>
@@ -4737,7 +4813,7 @@
       <c r="O7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="21">
+      <c r="P7" s="16">
         <f>O7/N7</f>
         <v/>
       </c>
@@ -4765,9 +4841,9 @@
         <v>1</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="21">
+        <v>1</v>
+      </c>
+      <c r="F8" s="16">
         <f>E8/D8</f>
         <v/>
       </c>
@@ -4775,9 +4851,9 @@
         <v>3</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="21">
+        <v>1</v>
+      </c>
+      <c r="I8" s="16">
         <f>H8/G8</f>
         <v/>
       </c>
@@ -4788,9 +4864,9 @@
         <v>2</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="21">
+        <v>1</v>
+      </c>
+      <c r="M8" s="16">
         <f>L8/K8</f>
         <v/>
       </c>
@@ -4798,9 +4874,9 @@
         <v>4</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="21">
+        <v>1</v>
+      </c>
+      <c r="P8" s="16">
         <f>O8/N8</f>
         <v/>
       </c>
@@ -4830,7 +4906,7 @@
       <c r="E9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="16">
         <f>E9/D9</f>
         <v/>
       </c>
@@ -4840,7 +4916,7 @@
       <c r="H9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="16">
         <f>H9/G9</f>
         <v/>
       </c>
@@ -4853,7 +4929,7 @@
       <c r="L9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="21">
+      <c r="M9" s="16">
         <f>L9/K9</f>
         <v/>
       </c>
@@ -4863,7 +4939,7 @@
       <c r="O9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="21">
+      <c r="P9" s="16">
         <f>O9/N9</f>
         <v/>
       </c>
@@ -4893,7 +4969,7 @@
       <c r="E10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="16">
         <f>E10/D10</f>
         <v/>
       </c>
@@ -4903,7 +4979,7 @@
       <c r="H10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="16">
         <f>H10/G10</f>
         <v/>
       </c>
@@ -4916,7 +4992,7 @@
       <c r="L10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="21">
+      <c r="M10" s="16">
         <f>L10/K10</f>
         <v/>
       </c>
@@ -4926,7 +5002,7 @@
       <c r="O10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="21">
+      <c r="P10" s="16">
         <f>O10/N10</f>
         <v/>
       </c>
@@ -4956,7 +5032,7 @@
       <c r="E11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="16">
         <f>E11/D11</f>
         <v/>
       </c>
@@ -4966,7 +5042,7 @@
       <c r="H11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="16">
         <f>H11/G11</f>
         <v/>
       </c>
@@ -4979,7 +5055,7 @@
       <c r="L11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="21">
+      <c r="M11" s="16">
         <f>L11/K11</f>
         <v/>
       </c>
@@ -4989,7 +5065,7 @@
       <c r="O11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="21">
+      <c r="P11" s="16">
         <f>O11/N11</f>
         <v/>
       </c>
@@ -4998,54 +5074,66 @@
       </c>
     </row>
     <row r="12" ht="16" customHeight="1" s="25">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
       <c r="B12" s="28" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16">
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20">
         <f>SUM(D3:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="22">
+      <c r="E12" s="20">
+        <f>SUM(E3:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="17">
         <f>E12/D12</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="20">
         <f>SUM(G3:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="22">
+      <c r="H12" s="20">
+        <f>SUM(H3:H11)</f>
+        <v/>
+      </c>
+      <c r="I12" s="17">
         <f>H12/G12</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="20">
         <f>SUM(J3:J11)</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="20">
         <f>SUM(K3:K11)</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
-      <c r="M12" s="22">
+      <c r="L12" s="20">
+        <f>SUM(L3:L11)</f>
+        <v/>
+      </c>
+      <c r="M12" s="17">
         <f>L12/K12</f>
         <v/>
       </c>
-      <c r="N12" s="16">
+      <c r="N12" s="20">
         <f>SUM(N3:N11)</f>
         <v/>
       </c>
-      <c r="O12" s="16" t="n"/>
-      <c r="P12" s="22">
+      <c r="O12" s="20">
+        <f>SUM(O3:O11)</f>
+        <v/>
+      </c>
+      <c r="P12" s="17">
         <f>O12/N12</f>
         <v/>
       </c>
-      <c r="Q12" s="16">
+      <c r="Q12" s="20">
         <f>SUM(Q3:Q11)</f>
         <v/>
       </c>
@@ -5068,7 +5156,7 @@
       <c r="E13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="16">
         <f>E13/D13</f>
         <v/>
       </c>
@@ -5078,7 +5166,7 @@
       <c r="H13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="16">
         <f>H13/G13</f>
         <v/>
       </c>
@@ -5091,7 +5179,7 @@
       <c r="L13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="21">
+      <c r="M13" s="16">
         <f>L13/K13</f>
         <v/>
       </c>
@@ -5101,7 +5189,7 @@
       <c r="O13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="21">
+      <c r="P13" s="16">
         <f>O13/N13</f>
         <v/>
       </c>
@@ -5127,7 +5215,7 @@
       <c r="E14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="16">
         <f>E14/D14</f>
         <v/>
       </c>
@@ -5137,7 +5225,7 @@
       <c r="H14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="16">
         <f>H14/G14</f>
         <v/>
       </c>
@@ -5150,7 +5238,7 @@
       <c r="L14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="21">
+      <c r="M14" s="16">
         <f>L14/K14</f>
         <v/>
       </c>
@@ -5160,7 +5248,7 @@
       <c r="O14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="21">
+      <c r="P14" s="16">
         <f>O14/N14</f>
         <v/>
       </c>
@@ -5190,7 +5278,7 @@
       <c r="E15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="16">
         <f>E15/D15</f>
         <v/>
       </c>
@@ -5200,7 +5288,7 @@
       <c r="H15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="16">
         <f>H15/G15</f>
         <v/>
       </c>
@@ -5211,9 +5299,9 @@
         <v>2</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="21">
+        <v>2</v>
+      </c>
+      <c r="M15" s="16">
         <f>L15/K15</f>
         <v/>
       </c>
@@ -5221,9 +5309,9 @@
         <v>5</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="21">
+        <v>2</v>
+      </c>
+      <c r="P15" s="16">
         <f>O15/N15</f>
         <v/>
       </c>
@@ -5253,7 +5341,7 @@
       <c r="E16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="16">
         <f>E16/D16</f>
         <v/>
       </c>
@@ -5263,7 +5351,7 @@
       <c r="H16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="16">
         <f>H16/G16</f>
         <v/>
       </c>
@@ -5274,9 +5362,9 @@
         <v>1</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="21">
+        <v>4</v>
+      </c>
+      <c r="M16" s="16">
         <f>L16/K16</f>
         <v/>
       </c>
@@ -5284,9 +5372,9 @@
         <v>2</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="21">
+        <v>4</v>
+      </c>
+      <c r="P16" s="16">
         <f>O16/N16</f>
         <v/>
       </c>
@@ -5314,9 +5402,9 @@
         <v>2</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="21">
+        <v>1</v>
+      </c>
+      <c r="F17" s="16">
         <f>E17/D17</f>
         <v/>
       </c>
@@ -5324,9 +5412,9 @@
         <v>5</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="21">
+        <v>1</v>
+      </c>
+      <c r="I17" s="16">
         <f>H17/G17</f>
         <v/>
       </c>
@@ -5339,7 +5427,7 @@
       <c r="L17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="21">
+      <c r="M17" s="16">
         <f>L17/K17</f>
         <v/>
       </c>
@@ -5349,7 +5437,7 @@
       <c r="O17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P17" s="21">
+      <c r="P17" s="16">
         <f>O17/N17</f>
         <v/>
       </c>
@@ -5375,7 +5463,7 @@
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="16">
         <f>E18/D18</f>
         <v/>
       </c>
@@ -5385,7 +5473,7 @@
       <c r="H18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="21">
+      <c r="I18" s="16">
         <f>H18/G18</f>
         <v/>
       </c>
@@ -5396,9 +5484,9 @@
         <v>1</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="21">
+        <v>1</v>
+      </c>
+      <c r="M18" s="16">
         <f>L18/K18</f>
         <v/>
       </c>
@@ -5406,9 +5494,9 @@
         <v>2</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="21">
+        <v>1</v>
+      </c>
+      <c r="P18" s="16">
         <f>O18/N18</f>
         <v/>
       </c>
@@ -5434,7 +5522,7 @@
       <c r="E19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="16">
         <f>E19/D19</f>
         <v/>
       </c>
@@ -5444,7 +5532,7 @@
       <c r="H19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="16">
         <f>H19/G19</f>
         <v/>
       </c>
@@ -5457,7 +5545,7 @@
       <c r="L19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="21">
+      <c r="M19" s="16">
         <f>L19/K19</f>
         <v/>
       </c>
@@ -5467,7 +5555,7 @@
       <c r="O19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="21">
+      <c r="P19" s="16">
         <f>O19/N19</f>
         <v/>
       </c>
@@ -5491,9 +5579,9 @@
         <v>1</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="21">
+        <v>1</v>
+      </c>
+      <c r="F20" s="16">
         <f>E20/D20</f>
         <v/>
       </c>
@@ -5501,9 +5589,9 @@
         <v>1</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="21">
+        <v>1</v>
+      </c>
+      <c r="I20" s="16">
         <f>H20/G20</f>
         <v/>
       </c>
@@ -5516,7 +5604,7 @@
       <c r="L20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="21">
+      <c r="M20" s="16">
         <f>L20/K20</f>
         <v/>
       </c>
@@ -5526,7 +5614,7 @@
       <c r="O20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P20" s="21">
+      <c r="P20" s="16">
         <f>O20/N20</f>
         <v/>
       </c>
@@ -5552,7 +5640,7 @@
       <c r="E21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="16">
         <f>E21/D21</f>
         <v/>
       </c>
@@ -5562,7 +5650,7 @@
       <c r="H21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="21">
+      <c r="I21" s="16">
         <f>H21/G21</f>
         <v/>
       </c>
@@ -5573,9 +5661,9 @@
         <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="21">
+        <v>1</v>
+      </c>
+      <c r="M21" s="16">
         <f>L21/K21</f>
         <v/>
       </c>
@@ -5583,9 +5671,9 @@
         <v>1</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="21">
+        <v>1</v>
+      </c>
+      <c r="P21" s="16">
         <f>O21/N21</f>
         <v/>
       </c>
@@ -5611,7 +5699,7 @@
       <c r="E22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="16">
         <f>E22/D22</f>
         <v/>
       </c>
@@ -5621,7 +5709,7 @@
       <c r="H22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="16">
         <f>H22/G22</f>
         <v/>
       </c>
@@ -5634,7 +5722,7 @@
       <c r="L22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="21">
+      <c r="M22" s="16">
         <f>L22/K22</f>
         <v/>
       </c>
@@ -5644,7 +5732,7 @@
       <c r="O22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="P22" s="21">
+      <c r="P22" s="16">
         <f>O22/N22</f>
         <v/>
       </c>
@@ -5653,54 +5741,66 @@
       </c>
     </row>
     <row r="23" ht="16" customHeight="1" s="25">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
       <c r="B23" s="28" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16">
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20">
         <f>SUM(D14:D22)</f>
         <v/>
       </c>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="22">
+      <c r="E23" s="20">
+        <f>SUM(E14:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="17">
         <f>E23/D23</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="20">
         <f>SUM(G14:G22)</f>
         <v/>
       </c>
-      <c r="H23" s="16" t="n"/>
-      <c r="I23" s="22">
+      <c r="H23" s="20">
+        <f>SUM(H14:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="17">
         <f>H23/G23</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="20">
         <f>SUM(J14:J22)</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="20">
         <f>SUM(K14:K22)</f>
         <v/>
       </c>
-      <c r="L23" s="16" t="n"/>
-      <c r="M23" s="22">
+      <c r="L23" s="20">
+        <f>SUM(L14:L22)</f>
+        <v/>
+      </c>
+      <c r="M23" s="17">
         <f>L23/K23</f>
         <v/>
       </c>
-      <c r="N23" s="16">
+      <c r="N23" s="20">
         <f>SUM(N14:N22)</f>
         <v/>
       </c>
-      <c r="O23" s="16" t="n"/>
-      <c r="P23" s="22">
+      <c r="O23" s="20">
+        <f>SUM(O14:O22)</f>
+        <v/>
+      </c>
+      <c r="P23" s="17">
         <f>O23/N23</f>
         <v/>
       </c>
-      <c r="Q23" s="16">
+      <c r="Q23" s="20">
         <f>SUM(Q14:Q22)</f>
         <v/>
       </c>
